--- a/04_DESIGN_TABLES/DesignTable_5405_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5405_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF27"/>
+  <dimension ref="A1:AF32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,17 +1141,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5405-04-04</t>
+          <t>5405-04-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="C7" t="n">
-        <v>0.43301</v>
+        <v>0.36084</v>
       </c>
       <c r="D7" t="n">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="E7" t="n">
         <v>0.26092</v>
@@ -1181,43 +1181,43 @@
         <v>0.21647</v>
       </c>
       <c r="N7" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="O7" t="n">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="P7" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0556</v>
+        <v>0.037</v>
       </c>
       <c r="S7" t="n">
-        <v>0.215</v>
+        <v>0.165</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2594</v>
+        <v>0.1946</v>
       </c>
       <c r="U7" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0.28</v>
+        <v>0.281</v>
       </c>
       <c r="W7" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>5405-04-04</t>
+          <t>5405-04-02</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 1/4-18 NPTF x 1/4-18 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1/4-18 NPTF x 1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1242,29 +1242,34 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Air-Way s85 only (no MS sheet exists for this topology); double-pass 28 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-04-02 col "L LGTH" = "1.220" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 227.5, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 22/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (6 differ, e.g. 5405-08-06 1.87 vs 1.66); CHEX@HEX: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-04-02 col "C HEX" = "0.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 227.5, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-08-16 1.38 vs 1.625); D@BORE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-04-02 col "A1 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 227.5, page verified) [Brennan = yes 2026-10-18] - male-end bore (to the pocket); mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-16-08 0.94 vs 0.697); TAPDRILL@BORE: end library gen_straight2 FPT[2] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.33, FPT_P1 0.46 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (male end); THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/8 NPT basic dimensions = tools_new/generators/ms51500.NPTF[2] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (female end); $PRP@Threads: thread texts from the part-number dashes, format of the built 5405 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex / D from the Brennan TFA catalog p12 alone; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>5405-04-04</t>
+          <t>5405-04-02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5405-04-06</t>
+          <t>5405-04-04</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="C8" t="n">
-        <v>0.50807</v>
+        <v>0.43301</v>
       </c>
       <c r="D8" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="E8" t="n">
         <v>0.26092</v>
@@ -1294,43 +1299,43 @@
         <v>0.21647</v>
       </c>
       <c r="N8" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="O8" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="P8" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="R8" t="n">
         <v>0.0556</v>
       </c>
       <c r="S8" t="n">
-        <v>0.285</v>
+        <v>0.215</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3294</v>
+        <v>0.2594</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="V8" t="n">
         <v>0.28</v>
       </c>
       <c r="W8" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5405-04-06</t>
+          <t>5405-04-04</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 1/4-18 NPTF x 3/8-18 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1/4-18 NPTF x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1345,7 +1350,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1360,24 +1365,24 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>5405-04-06</t>
+          <t>5405-04-04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5405-04-08</t>
+          <t>5405-04-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="C9" t="n">
-        <v>0.65241</v>
+        <v>0.50807</v>
       </c>
       <c r="D9" t="n">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="E9" t="n">
         <v>0.26092</v>
@@ -1407,43 +1412,43 @@
         <v>0.21647</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="R9" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="S9" t="n">
-        <v>0.35</v>
+        <v>0.285</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4071</v>
+        <v>0.3294</v>
       </c>
       <c r="U9" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
         <v>0.28</v>
       </c>
       <c r="W9" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5405-04-08</t>
+          <t>5405-04-06</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 1/4-18 NPTF x 1/2-14 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1/4-18 NPTF x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1458,7 +1463,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1473,90 +1478,90 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>5405-04-08</t>
+          <t>5405-04-06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5405-06-04</t>
+          <t>5405-04-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="C10" t="n">
-        <v>0.43301</v>
+        <v>0.65241</v>
       </c>
       <c r="D10" t="n">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="G10" t="n">
         <v>1.7899</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1522</v>
+        <v>0.1582</v>
       </c>
       <c r="I10" t="n">
-        <v>0.65645</v>
+        <v>0.52183</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="K10" t="n">
         <v>0.05556</v>
       </c>
       <c r="L10" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="M10" t="n">
-        <v>0.28378</v>
+        <v>0.21647</v>
       </c>
       <c r="N10" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="O10" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0556</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>0.285</v>
+        <v>0.35</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3294</v>
+        <v>0.4071</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="V10" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="W10" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>5405-06-04</t>
+          <t>5405-04-08</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 3/8-18 NPTF x 1/4-18 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1/4-18 NPTF x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1566,12 +1571,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1586,90 +1591,90 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>5405-06-04</t>
+          <t>5405-04-08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5405-06-06</t>
+          <t>5405-04-12</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="C11" t="n">
-        <v>0.50807</v>
+        <v>0.79386</v>
       </c>
       <c r="D11" t="n">
-        <v>0.88</v>
+        <v>1.375</v>
       </c>
       <c r="E11" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="G11" t="n">
         <v>1.7899</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1522</v>
+        <v>0.1582</v>
       </c>
       <c r="I11" t="n">
-        <v>0.65645</v>
+        <v>0.52183</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="K11" t="n">
         <v>0.05556</v>
       </c>
       <c r="L11" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="M11" t="n">
-        <v>0.28378</v>
+        <v>0.21647</v>
       </c>
       <c r="N11" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="O11" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="P11" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0556</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>0.285</v>
+        <v>0.455</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3294</v>
+        <v>0.5121</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
-        <v>0.41</v>
+        <v>0.281</v>
       </c>
       <c r="W11" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>5405-06-06</t>
+          <t>5405-04-12</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 3/8-18 NPTF x 3/8-18 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1/4-18 NPTF x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1679,12 +1684,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1694,29 +1699,34 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Air-Way s85 only (no MS sheet exists for this topology); double-pass 28 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-04-12 col "L LGTH" = "1.74" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 267.8, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 22/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (6 differ, e.g. 5405-08-06 1.87 vs 1.66); CHEX@HEX: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-04-12 col "C HEX" = "1.375" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 267.8, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-08-16 1.38 vs 1.625); D@BORE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-04-12 col "A1 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 267.8, page verified) [Brennan = yes 2026-10-18] - male-end bore (to the pocket); mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-16-08 0.94 vs 0.697); TAPDRILL@BORE: end library gen_straight2 FPT[12] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.91, FPT_P1 0.91 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (male end); THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (female end); $PRP@Threads: thread texts from the part-number dashes, format of the built 5405 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex / D from the Brennan TFA catalog p12 alone; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>5405-06-06</t>
+          <t>5405-04-12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5405-06-08</t>
+          <t>5405-06-04</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="C12" t="n">
-        <v>0.65241</v>
+        <v>0.43301</v>
       </c>
       <c r="D12" t="n">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="E12" t="n">
         <v>0.32823</v>
@@ -1746,43 +1756,43 @@
         <v>0.28378</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="R12" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="S12" t="n">
-        <v>0.35</v>
+        <v>0.285</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4071</v>
+        <v>0.3294</v>
       </c>
       <c r="U12" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
         <v>0.41</v>
       </c>
       <c r="W12" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5405-06-08</t>
+          <t>5405-06-04</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 3/8-18 NPTF x 1/2-14 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 3/8-18 NPTF x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1797,7 +1807,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1812,24 +1822,24 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>5405-06-08</t>
+          <t>5405-06-04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5405-06-12</t>
+          <t>5405-06-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="C13" t="n">
-        <v>0.79674</v>
+        <v>0.50807</v>
       </c>
       <c r="D13" t="n">
-        <v>1.38</v>
+        <v>0.88</v>
       </c>
       <c r="E13" t="n">
         <v>0.32823</v>
@@ -1859,43 +1869,43 @@
         <v>0.28378</v>
       </c>
       <c r="N13" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="O13" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="P13" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="R13" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="S13" t="n">
-        <v>0.455</v>
+        <v>0.285</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5121</v>
+        <v>0.3294</v>
       </c>
       <c r="U13" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
         <v>0.41</v>
       </c>
       <c r="W13" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5405-06-12</t>
+          <t>5405-06-06</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 3/8-18 NPTF x 3/4-14 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 3/8-18 NPTF x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -1910,7 +1920,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1925,90 +1935,90 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>5405-06-12</t>
+          <t>5405-06-06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5405-08-06</t>
+          <t>5405-06-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="C14" t="n">
-        <v>0.50807</v>
+        <v>0.65241</v>
       </c>
       <c r="D14" t="n">
-        <v>0.88</v>
+        <v>1.13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="G14" t="n">
         <v>1.7899</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2163</v>
+        <v>0.1522</v>
       </c>
       <c r="I14" t="n">
-        <v>0.81557</v>
+        <v>0.65645</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="K14" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="L14" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="M14" t="n">
-        <v>0.35064</v>
+        <v>0.28378</v>
       </c>
       <c r="N14" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="O14" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="P14" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0556</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>0.285</v>
+        <v>0.35</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3294</v>
+        <v>0.4071</v>
       </c>
       <c r="U14" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="V14" t="n">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>0.78</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>5405-08-06</t>
+          <t>5405-06-08</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 1/2-14 NPTF x 3/8-18 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 3/8-18 NPTF x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2018,12 +2028,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2038,18 +2048,18 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>5405-08-06</t>
+          <t>5405-06-08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5405-08-12</t>
+          <t>5405-06-12</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="C15" t="n">
         <v>0.79674</v>
@@ -2058,31 +2068,31 @@
         <v>1.38</v>
       </c>
       <c r="E15" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="G15" t="n">
         <v>1.7899</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2163</v>
+        <v>0.1522</v>
       </c>
       <c r="I15" t="n">
-        <v>0.81557</v>
+        <v>0.65645</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="K15" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="L15" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="M15" t="n">
-        <v>0.35064</v>
+        <v>0.28378</v>
       </c>
       <c r="N15" t="n">
         <v>0.91</v>
@@ -2106,22 +2116,22 @@
         <v>0.5121</v>
       </c>
       <c r="U15" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="V15" t="n">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>0.83</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>5405-08-12</t>
+          <t>5405-06-12</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 1/2-14 NPTF x 3/4-14 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 3/8-18 NPTF x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2131,7 +2141,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2151,90 +2161,90 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>5405-08-12</t>
+          <t>5405-06-12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5405-12-08</t>
+          <t>5405-08-04</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="C16" t="n">
-        <v>0.65241</v>
+        <v>0.50518</v>
       </c>
       <c r="D16" t="n">
-        <v>1.13</v>
+        <v>0.875</v>
       </c>
       <c r="E16" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="G16" t="n">
         <v>1.7899</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2043</v>
+        <v>0.2163</v>
       </c>
       <c r="I16" t="n">
-        <v>1.02482</v>
+        <v>0.81557</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="K16" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="M16" t="n">
-        <v>0.45527</v>
+        <v>0.35064</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="R16" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="S16" t="n">
-        <v>0.35</v>
+        <v>0.215</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4071</v>
+        <v>0.2594</v>
       </c>
       <c r="U16" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>0.72</v>
+        <v>0.531</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>5405-12-08</t>
+          <t>5405-08-04</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 3/4-14 NPTF x 1/2-14 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1/2-14 NPTF x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2244,12 +2254,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2259,100 +2269,100 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Air-Way s85 only (no MS sheet exists for this topology); double-pass 28 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-08-04 col "L LGTH" = "1.640" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 338.4, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 22/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (6 differ, e.g. 5405-08-06 1.87 vs 1.66); CHEX@HEX: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-08-04 col "C HEX" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 338.4, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-08-16 1.38 vs 1.625); D@BORE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-08-04 col "A1 DRILL" = "0.531" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 338.4, page verified) [Brennan = yes 2026-10-18] - male-end bore (to the pocket); mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-16-08 0.94 vs 0.697); TAPDRILL@BORE: end library gen_straight2 FPT[4] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.43, FPT_P1 0.67 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[8] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (male end); THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (female end); $PRP@Threads: thread texts from the part-number dashes, format of the built 5405 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>ASSUMPTION: Air-Way bore D 0.72 is wider than the port tap drill 0.7 - the bore stops at the port bottom, leaving a 0.010 internal step there (real part unconfirmed)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex / D from the Brennan TFA catalog p12 alone; tap drill = Air-Way per size (A1 yes) | ASSUMPTION: Air-Way bore D 0.531 is wider than the port tap drill 0.43 - the bore stops at the port bottom, leaving a 0.051 internal step there (real part unconfirmed)</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>5405-12-08</t>
+          <t>5405-08-04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5405-12-12</t>
+          <t>5405-08-06</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="C17" t="n">
-        <v>0.79674</v>
+        <v>0.50807</v>
       </c>
       <c r="D17" t="n">
-        <v>1.38</v>
+        <v>0.88</v>
       </c>
       <c r="E17" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="G17" t="n">
         <v>1.7899</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2043</v>
+        <v>0.2163</v>
       </c>
       <c r="I17" t="n">
-        <v>1.02482</v>
+        <v>0.81557</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="K17" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="M17" t="n">
-        <v>0.45527</v>
+        <v>0.35064</v>
       </c>
       <c r="N17" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="O17" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="P17" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="R17" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="S17" t="n">
-        <v>0.455</v>
+        <v>0.285</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5121</v>
+        <v>0.3294</v>
       </c>
       <c r="U17" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="V17" t="n">
-        <v>0.72</v>
+        <v>0.53</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>5405-12-12</t>
+          <t>5405-08-06</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 3/4-14 NPTF x 3/4-14 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1/2-14 NPTF x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2362,12 +2372,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2382,90 +2392,90 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>5405-12-12</t>
+          <t>5405-08-06</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5405-12-16</t>
+          <t>5405-08-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="C18" t="n">
-        <v>0.94108</v>
+        <v>0.79674</v>
       </c>
       <c r="D18" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="E18" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="G18" t="n">
         <v>1.7899</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2043</v>
+        <v>0.2163</v>
       </c>
       <c r="I18" t="n">
-        <v>1.02482</v>
+        <v>0.81557</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="K18" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="M18" t="n">
-        <v>0.45527</v>
+        <v>0.35064</v>
       </c>
       <c r="N18" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="O18" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="P18" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="R18" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>0.57</v>
+        <v>0.455</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.5121</v>
       </c>
       <c r="U18" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="V18" t="n">
-        <v>0.72</v>
+        <v>0.53</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>5405-12-16</t>
+          <t>5405-08-12</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 3/4-14 NPTF x 1-11 1/2 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1/2-14 NPTF x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2475,12 +2485,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2495,24 +2505,24 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>5405-12-16</t>
+          <t>5405-08-12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5405-12-20</t>
+          <t>5405-12-08</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1547</v>
+        <v>0.65241</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1.13</v>
       </c>
       <c r="E19" t="n">
         <v>0.51241</v>
@@ -2542,43 +2552,43 @@
         <v>0.45527</v>
       </c>
       <c r="N19" t="n">
-        <v>1.48</v>
+        <v>0.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.16</v>
+        <v>0.9</v>
       </c>
       <c r="P19" t="n">
-        <v>1.48</v>
+        <v>0.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.16</v>
+        <v>0.9</v>
       </c>
       <c r="R19" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>0.74</v>
+        <v>0.35</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8096</v>
+        <v>0.4071</v>
       </c>
       <c r="U19" t="n">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="V19" t="n">
         <v>0.72</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>5405-12-20</t>
+          <t>5405-12-08</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 3/4-14 NPTF x 1 1/4-11 1/2 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 3/4-14 NPTF x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2593,7 +2603,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2606,20 +2616,25 @@
           <t>Air-Way s85 only (no MS sheet exists for this topology); double-pass 28 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
         </is>
       </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>ASSUMPTION: Air-Way bore D 0.72 is wider than the port tap drill 0.7 - the bore stops at the port bottom, leaving a 0.010 internal step there (real part unconfirmed)</t>
+        </is>
+      </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>5405-12-20</t>
+          <t>5405-12-08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5405-16-08</t>
+          <t>5405-12-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.37</v>
+        <v>1.93</v>
       </c>
       <c r="C20" t="n">
         <v>0.79674</v>
@@ -2628,70 +2643,70 @@
         <v>1.38</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="G20" t="n">
         <v>1.7899</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2572</v>
+        <v>0.2043</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2832</v>
+        <v>1.02482</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="M20" t="n">
-        <v>0.57203</v>
+        <v>0.45527</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="R20" t="n">
         <v>0.07140000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>0.35</v>
+        <v>0.455</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4071</v>
+        <v>0.5121</v>
       </c>
       <c r="U20" t="n">
-        <v>2.37</v>
+        <v>1.93</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="W20" t="n">
-        <v>1.47</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>5405-16-08</t>
+          <t>5405-12-12</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 1-11 1/2 NPTF x 1/2-14 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 3/4-14 NPTF x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2701,12 +2716,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2719,97 +2734,92 @@
           <t>Air-Way s85 only (no MS sheet exists for this topology); double-pass 28 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>ASSUMPTION: Air-Way bore D 0.94 is wider than the port tap drill 0.7 - the bore stops at the port bottom, leaving a 0.120 internal step there (real part unconfirmed)</t>
-        </is>
-      </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>5405-16-08</t>
+          <t>5405-12-12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5405-16-12</t>
+          <t>5405-12-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="C21" t="n">
-        <v>0.79674</v>
+        <v>0.94108</v>
       </c>
       <c r="D21" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="G21" t="n">
         <v>1.7899</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2572</v>
+        <v>0.2043</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2832</v>
+        <v>1.02482</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="K21" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="M21" t="n">
-        <v>0.57203</v>
+        <v>0.45527</v>
       </c>
       <c r="N21" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="O21" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="P21" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="R21" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>0.455</v>
+        <v>0.57</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5121</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="W21" t="n">
-        <v>1.46</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>5405-16-12</t>
+          <t>5405-12-16</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 1-11 1/2 NPTF x 3/4-14 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 3/4-14 NPTF x 1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2819,12 +2829,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2837,97 +2847,92 @@
           <t>Air-Way s85 only (no MS sheet exists for this topology); double-pass 28 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>ASSUMPTION: Air-Way bore D 0.94 is wider than the port tap drill 0.91 - the bore stops at the port bottom, leaving a 0.015 internal step there (real part unconfirmed)</t>
-        </is>
-      </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>5405-16-12</t>
+          <t>5405-12-16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5405-16-16</t>
+          <t>5405-12-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="C22" t="n">
-        <v>0.94108</v>
+        <v>1.1547</v>
       </c>
       <c r="D22" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="G22" t="n">
         <v>1.7899</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2572</v>
+        <v>0.2043</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2832</v>
+        <v>1.02482</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="K22" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="M22" t="n">
-        <v>0.57203</v>
+        <v>0.45527</v>
       </c>
       <c r="N22" t="n">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
       <c r="O22" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P22" t="n">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="R22" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>0.57</v>
+        <v>0.74</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.8096</v>
       </c>
       <c r="U22" t="n">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>5405-16-16</t>
+          <t>5405-12-20</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 1-11 1/2 NPTF x 1-11 1/2 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 3/4-14 NPTF x 1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -2937,12 +2942,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -2957,24 +2962,24 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>5405-16-16</t>
+          <t>5405-12-20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5405-16-20</t>
+          <t>5405-16-08</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1547</v>
+        <v>0.79674</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="E23" t="n">
         <v>0.6415999999999999</v>
@@ -3004,43 +3009,43 @@
         <v>0.57203</v>
       </c>
       <c r="N23" t="n">
-        <v>1.48</v>
+        <v>0.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.16</v>
+        <v>0.9</v>
       </c>
       <c r="P23" t="n">
-        <v>1.48</v>
+        <v>0.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.16</v>
+        <v>0.9</v>
       </c>
       <c r="R23" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>0.74</v>
+        <v>0.35</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8096</v>
+        <v>0.4071</v>
       </c>
       <c r="U23" t="n">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="V23" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>5405-16-20</t>
+          <t>5405-16-08</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 1-11 1/2 NPTF x 1 1/4-11 1/2 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1-11 1/2 NPTF x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3055,7 +3060,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3068,92 +3073,97 @@
           <t>Air-Way s85 only (no MS sheet exists for this topology); double-pass 28 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
         </is>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>ASSUMPTION: Air-Way bore D 0.94 is wider than the port tap drill 0.7 - the bore stops at the port bottom, leaving a 0.120 internal step there (real part unconfirmed)</t>
+        </is>
+      </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>5405-16-20</t>
+          <t>5405-16-08</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5405-20-24</t>
+          <t>5405-16-12</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="C24" t="n">
-        <v>1.37409</v>
+        <v>0.79674</v>
       </c>
       <c r="D24" t="n">
-        <v>2.38</v>
+        <v>1.38</v>
       </c>
       <c r="E24" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="G24" t="n">
         <v>1.7899</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2632</v>
+        <v>0.2572</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6267</v>
+        <v>1.2832</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="K24" t="n">
         <v>0.08696</v>
       </c>
       <c r="L24" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>0.74378</v>
+        <v>0.57203</v>
       </c>
       <c r="N24" t="n">
-        <v>1.72</v>
+        <v>0.91</v>
       </c>
       <c r="O24" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="P24" t="n">
-        <v>1.72</v>
+        <v>0.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="R24" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>0.86</v>
+        <v>0.455</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9296</v>
+        <v>0.5121</v>
       </c>
       <c r="U24" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="V24" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>5405-20-24</t>
+          <t>5405-16-12</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 1 1/4-11 1/2 NPTF x 1 1/2-11 1/2 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1-11 1/2 NPTF x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3163,12 +3173,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3181,92 +3191,97 @@
           <t>Air-Way s85 only (no MS sheet exists for this topology); double-pass 28 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
         </is>
       </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>ASSUMPTION: Air-Way bore D 0.94 is wider than the port tap drill 0.91 - the bore stops at the port bottom, leaving a 0.015 internal step there (real part unconfirmed)</t>
+        </is>
+      </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>5405-20-24</t>
+          <t>5405-16-12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5405-24-24</t>
+          <t>5405-16-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="C25" t="n">
-        <v>1.37409</v>
+        <v>0.94108</v>
       </c>
       <c r="D25" t="n">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="E25" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="G25" t="n">
         <v>1.7899</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2765</v>
+        <v>0.2572</v>
       </c>
       <c r="I25" t="n">
-        <v>1.86566</v>
+        <v>1.2832</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="K25" t="n">
         <v>0.08696</v>
       </c>
       <c r="L25" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>0.86326</v>
+        <v>0.57203</v>
       </c>
       <c r="N25" t="n">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="O25" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P25" t="n">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="R25" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9296</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="V25" t="n">
-        <v>1.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>5405-24-24</t>
+          <t>5405-16-16</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 1 1/2-11 1/2 NPTF x 1 1/2-11 1/2 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1-11 1/2 NPTF x 1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3276,12 +3291,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF (female)</t>
+          <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3296,90 +3311,90 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>5405-24-24</t>
+          <t>5405-16-16</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5405-24-32</t>
+          <t>5405-16-20</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="C26" t="n">
-        <v>1.66277</v>
+        <v>1.1547</v>
       </c>
       <c r="D26" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="G26" t="n">
         <v>1.7899</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2765</v>
+        <v>0.2572</v>
       </c>
       <c r="I26" t="n">
-        <v>1.86566</v>
+        <v>1.2832</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="K26" t="n">
         <v>0.08696</v>
       </c>
       <c r="L26" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>0.86326</v>
+        <v>0.57203</v>
       </c>
       <c r="N26" t="n">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="O26" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P26" t="n">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="R26" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>1.095</v>
+        <v>0.74</v>
       </c>
       <c r="T26" t="n">
-        <v>1.1646</v>
+        <v>0.8096</v>
       </c>
       <c r="U26" t="n">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="V26" t="n">
-        <v>1.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>5405-24-32</t>
+          <t>5405-16-20</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Pipe Adapter (male NPTF x female NPTF), 1 1/2-11 1/2 NPTF x 2-11 1/2 NPTF (female)</t>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1-11 1/2 NPTF x 1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3389,12 +3404,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2-11 1/2 NPTF (female)</t>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3409,123 +3424,698 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>5405-24-32</t>
+          <t>5405-16-20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5405-32-32</t>
+          <t>5405-20-20</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="C27" t="n">
-        <v>1.66277</v>
+        <v>1.1547</v>
       </c>
       <c r="D27" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="G27" t="n">
         <v>1.7899</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2735</v>
+        <v>0.2632</v>
       </c>
       <c r="I27" t="n">
-        <v>2.33859</v>
+        <v>1.6267</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="K27" t="n">
         <v>0.08696</v>
       </c>
       <c r="L27" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="M27" t="n">
-        <v>1.09973</v>
+        <v>0.74378</v>
       </c>
       <c r="N27" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="O27" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="R27" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="S27" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>5405-20-20</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1 1/4-11 1/2 NPTF x 1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>5405</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-20-20 col "L LGTH" = "2.49" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 509.8, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 22/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (6 differ, e.g. 5405-08-06 1.87 vs 1.66); CHEX@HEX: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-20-20 col "C HEX" = "2.000" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 509.8, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-08-16 1.38 vs 1.625); D@BORE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-20-20 col "A1 DRILL" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 509.8, page verified) [Brennan = yes 2026-10-18] - male-end bore (to the pocket); mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-16-08 0.94 vs 0.697); TAPDRILL@BORE: end library gen_straight2 FPT[20] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 1.48, FPT_P1 1.16 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (male end); THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (female end); $PRP@Threads: thread texts from the part-number dashes, format of the built 5405 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex / D from the Brennan TFA catalog p12 alone; tap drill = Air-Way per size (A1 yes)</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>5405-20-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5405-20-24</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.37409</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.9296</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>5405-20-24</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1 1/4-11 1/2 NPTF x 1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>5405</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Air-Way s85 only (no MS sheet exists for this topology); double-pass 28 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>5405-20-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>5405-24-20</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>5405-24-20</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1 1/2-11 1/2 NPTF x 1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>5405</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-24-20 col "L LGTH" = "2.540" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 540.0, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 22/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (6 differ, e.g. 5405-08-06 1.87 vs 1.66); CHEX@HEX: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-24-20 col "C HEX" = "2.000" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 540.0, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-08-16 1.38 vs 1.625); D@BORE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-24-20 col "A1 DRILL" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 540.0, page verified) [Brennan = yes 2026-10-18] - male-end bore (to the pocket); mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-16-08 0.94 vs 0.697); TAPDRILL@BORE: end library gen_straight2 FPT[20] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 1.48, FPT_P1 1.16 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (male end); THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (female end); $PRP@Threads: thread texts from the part-number dashes, format of the built 5405 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex / D from the Brennan TFA catalog p12 alone; tap drill = Air-Way per size (A1 yes) | ASSUMPTION: Air-Way bore D 1.5 is wider than the port tap drill 1.48 - the bore stops at the port bottom, leaving a 0.010 internal step there (real part unconfirmed)</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>5405-24-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5405-24-24</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.37409</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.9296</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>5405-24-24</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1 1/2-11 1/2 NPTF x 1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>5405</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Air-Way s85 only (no MS sheet exists for this topology); double-pass 28 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>5405-24-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>5405-24-32</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.1646</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>5405-24-32</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Pipe Adapter (male NPTF x female NPTF), 1 1/2-11 1/2 NPTF x 2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>5405</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Air-Way s85 only (no MS sheet exists for this topology); double-pass 28 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>5405-24-32</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5405-32-32</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="S32" t="n">
         <v>1.1</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T32" t="n">
         <v>1.1696</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U32" t="n">
         <v>2.66</v>
       </c>
-      <c r="V27" t="n">
+      <c r="V32" t="n">
         <v>1.94</v>
       </c>
-      <c r="W27" t="n">
+      <c r="W32" t="n">
         <v>1.48</v>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>5405-32-32</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Pipe Adapter (male NPTF x female NPTF), 2-11 1/2 NPTF x 2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>5405</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>Air-Way s85 only (no MS sheet exists for this topology); double-pass 28 rows | MODEL: NPTF male end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); female drill depth = MS51503 P1 max per pipe dash (2405 table), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D runs from the male tip to the pocket bottom</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>tap drill printed 2.20 (24-32 row prints 2.19 for same 2-11 1/2 thread) - as-printed</t>
         </is>
       </c>
-      <c r="AF27" t="inlineStr">
+      <c r="AF32" t="inlineStr">
         <is>
           <t>5405-32-32</t>
         </is>
